--- a/codigos/Codigos_resNet/datos/reservas.xlsx
+++ b/codigos/Codigos_resNet/datos/reservas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\codigos\Codigos_resNet\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86EAE6DC-6404-4A20-990C-2F670F61DD52}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3449C7AD-D28F-4143-A8FB-18CC312C5083}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C7579241-7489-40CF-9787-376B9A4A8E82}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -50,12 +50,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -98,11 +92,11 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -422,6 +416,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9EA03E-BBEF-4747-B6A9-8D828720BEF1}">
   <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">

--- a/codigos/Codigos_resNet/datos/reservas.xlsx
+++ b/codigos/Codigos_resNet/datos/reservas.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\codigos\Codigos_resNet\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3449C7AD-D28F-4143-A8FB-18CC312C5083}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE0FC77-CF67-431E-8D74-BF4C75119F29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C7579241-7489-40CF-9787-376B9A4A8E82}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -115,6 +118,94 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Reservas"/>
+      <sheetName val="Cuadro"/>
+      <sheetName val="M0"/>
+      <sheetName val="M1"/>
+      <sheetName val="M2"/>
+      <sheetName val="M3"/>
+      <sheetName val="M3_total"/>
+      <sheetName val="Observaciones"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1146">
+          <cell r="H1146">
+            <v>44601.93548387097</v>
+          </cell>
+        </row>
+        <row r="1147">
+          <cell r="H1147">
+            <v>45475.714285714283</v>
+          </cell>
+        </row>
+        <row r="1148">
+          <cell r="H1148" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1149">
+          <cell r="H1149" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1150">
+          <cell r="H1150" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1151">
+          <cell r="H1151" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1152">
+          <cell r="H1152" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1153">
+          <cell r="H1153" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1154">
+          <cell r="H1154" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1155">
+          <cell r="H1155" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1156">
+          <cell r="H1156" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="1157">
+          <cell r="H1157" t="str">
+            <v/>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9EA03E-BBEF-4747-B6A9-8D828720BEF1}">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
@@ -1009,7 +1100,107 @@
         <v>46023</v>
       </c>
       <c r="B74" s="1">
-        <v>44503</v>
+        <f>+[1]Reservas!$H1146</f>
+        <v>44601.93548387097</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B75" s="1">
+        <f>+[1]Reservas!$H1147</f>
+        <v>45475.714285714283</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B76" s="1" t="str">
+        <f>+[1]Reservas!$H1148</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B77" s="1" t="str">
+        <f>+[1]Reservas!$H1149</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B78" s="1" t="str">
+        <f>+[1]Reservas!$H1150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B79" s="1" t="str">
+        <f>+[1]Reservas!$H1151</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B80" s="1" t="str">
+        <f>+[1]Reservas!$H1152</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B81" s="1" t="str">
+        <f>+[1]Reservas!$H1153</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B82" s="1" t="str">
+        <f>+[1]Reservas!$H1154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B83" s="1" t="str">
+        <f>+[1]Reservas!$H1155</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2">
+        <v>46327</v>
+      </c>
+      <c r="B84" s="1" t="str">
+        <f>+[1]Reservas!$H1156</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2">
+        <v>46357</v>
+      </c>
+      <c r="B85" s="1" t="str">
+        <f>+[1]Reservas!$H1157</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/codigos/Codigos_resNet/datos/reservas.xlsx
+++ b/codigos/Codigos_resNet/datos/reservas.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\codigos\Codigos_resNet\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE0FC77-CF67-431E-8D74-BF4C75119F29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AC651A-8ACB-4CD8-A650-CEFA37395FE6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C7579241-7489-40CF-9787-376B9A4A8E82}"/>
+    <workbookView xWindow="30" yWindow="630" windowWidth="20460" windowHeight="10890" xr2:uid="{C7579241-7489-40CF-9787-376B9A4A8E82}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -145,16 +146,6 @@
             <v>45475.714285714283</v>
           </cell>
         </row>
-        <row r="1148">
-          <cell r="H1148" t="str">
-            <v/>
-          </cell>
-        </row>
-        <row r="1149">
-          <cell r="H1149" t="str">
-            <v/>
-          </cell>
-        </row>
         <row r="1150">
           <cell r="H1150" t="str">
             <v/>
@@ -203,6 +194,27 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Serie_diaria"/>
+      <sheetName val="Observaciones"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="87">
+          <cell r="D87">
+            <v>44248</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1117,18 +1129,17 @@
       <c r="A76" s="2">
         <v>46082</v>
       </c>
-      <c r="B76" s="1" t="str">
-        <f>+[1]Reservas!$H1148</f>
-        <v/>
+      <c r="B76" s="1">
+        <f>+[2]Serie_diaria!$D$87</f>
+        <v>44248</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
         <v>46113</v>
       </c>
-      <c r="B77" s="1" t="str">
-        <f>+[1]Reservas!$H1149</f>
-        <v/>
+      <c r="B77" s="1">
+        <v>42052</v>
       </c>
     </row>
     <row r="78" spans="1:2">
